--- a/src/attributions/attributions_ig_traj_101.xlsx
+++ b/src/attributions/attributions_ig_traj_101.xlsx
@@ -1002,22 +1002,22 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3108430823484841</v>
+        <v>0.7587071690244898</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.215279026913243</v>
+        <v>-0.3702869927365398</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04196797237908838</v>
+        <v>-0.1311692622175754</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -1026,82 +1026,82 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3788967844860385</v>
+        <v>1.169636149701462</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3869458032419404</v>
+        <v>-0.9639209061813845</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0150000989646639</v>
+        <v>-0.3579795192018522</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1361622821586091</v>
+        <v>0.3310818365230463</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01362004364599871</v>
+        <v>-0.05430880200213099</v>
       </c>
       <c r="W2" t="n">
-        <v>0.169290158519037</v>
+        <v>-0.08150385880266524</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.04679408994751928</v>
+        <v>0.05327375438979494</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-7.271395222594975e-05</v>
+        <v>-0.1002005103725624</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01536586175959912</v>
+        <v>0.02380139194911983</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0</v>
@@ -1110,70 +1110,70 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06644593466299445</v>
+        <v>0.6152848335477114</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.1231780516873787</v>
+        <v>-0.07719087276256698</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.03115460533775904</v>
+        <v>0.540616620933204</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.6582304629374546</v>
+        <v>1.500124097460607</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.1821602655752124</v>
+        <v>-0.5425899811491955</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3302382338368208</v>
+        <v>-0.499682627872634</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.008840646143726627</v>
+        <v>-0.1237792866362218</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.1087861787726551</v>
+        <v>-0.08718763465973808</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06266042071522059</v>
+        <v>-0.04189438373776567</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,28 +1182,28 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.06780809363976335</v>
+        <v>-0.2904942751436131</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.09302470027565145</v>
+        <v>0.03933712448591581</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1818579037297978</v>
+        <v>0.1024694309638673</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
@@ -1218,46 +1218,46 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.3343052278326771</v>
+        <v>0.963419675411668</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.05499268012581732</v>
+        <v>-0.4304870067623876</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1727270952047446</v>
+        <v>-0.1688608332452627</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1366080808194204</v>
+        <v>-0.6054983642435495</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1093618989008442</v>
+        <v>0.3582443179890918</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.07063789846302188</v>
+        <v>-0.01863700261299791</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
@@ -1272,22 +1272,22 @@
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01396565041065752</v>
+        <v>-0.3595731909063214</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.07883331400896461</v>
+        <v>0.2118900608760677</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.1804675003963667</v>
+        <v>0.07707893582411686</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>-0</v>
@@ -1296,28 +1296,28 @@
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1458073311854229</v>
+        <v>-0.6437760217623124</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.1343660873926265</v>
+        <v>0.363877889958857</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.05318477007954928</v>
+        <v>0.05081588387259828</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
@@ -1326,22 +1326,22 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1137320396913071</v>
+        <v>-0.5565766423720886</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.07563938390692801</v>
+        <v>0.4887617603782716</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.13111291396337</v>
+        <v>-0.2114285075245216</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.05240173340726712</v>
+        <v>-0.2336472313055225</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.04155841114477513</v>
+        <v>0.2625563648475069</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.05719448606205347</v>
+        <v>-0.3208610177324809</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
@@ -1380,25 +1380,25 @@
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.06927416601096098</v>
+        <v>0.2571622803167413</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.01033409817111543</v>
+        <v>0.2923375217449956</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02943521281237161</v>
+        <v>-0.05729844171228996</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1615718747876243</v>
+        <v>-0.5247195719267769</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.1564429457867083</v>
+        <v>0.293507377965065</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1235387854208232</v>
+        <v>0.06365064420102827</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,25 +1434,25 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1333499605723506</v>
+        <v>-0.4863090326086241</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.1690870356275521</v>
+        <v>0.1813841881895847</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.1569037627179171</v>
+        <v>0.1552553697625632</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,100 +1461,100 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1600689495630654</v>
+        <v>-0.7052838060923747</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.1194576770790843</v>
+        <v>0.4253732318255584</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.07435367569592584</v>
+        <v>0.01935478804644222</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01971502394635141</v>
+        <v>-0.2691912448158003</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.04891549222302669</v>
+        <v>0.0002870936601702218</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02429698130576186</v>
+        <v>-0.0945365765831116</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01626106828758994</v>
+        <v>-0.5122336869219569</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1064610122259297</v>
+        <v>0.6161941921871996</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.211432799785417</v>
+        <v>0.201434365575007</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.0551922460020129</v>
+        <v>-0.4838342749796555</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.05275749035174134</v>
+        <v>0.17165030515718</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1571,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.9045425121380398</v>
+        <v>-0.5053296779343865</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -1580,43 +1580,43 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1648810128891083</v>
+        <v>-0.04126826111582132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6318573321380593</v>
+        <v>0.1912645411478885</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6889828287296895</v>
+        <v>-0.5413366633245222</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09659910153713192</v>
+        <v>0.08213528602635116</v>
       </c>
       <c r="O3" t="n">
-        <v>0.761240692770956</v>
+        <v>0.2467974426471053</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>-0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2455069697333724</v>
+        <v>-0.1987675687274541</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
@@ -1634,10 +1634,10 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1674467064713038</v>
+        <v>0.1144320664779945</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08926734067128778</v>
+        <v>0.09680145382156777</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1646,13 +1646,13 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.07102624723401964</v>
+        <v>0.02615319622141804</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
@@ -1661,16 +1661,16 @@
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.03424110197480633</v>
+        <v>0.06320026948853114</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.06028947335712816</v>
+        <v>0.0192640074929136</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1679,22 +1679,22 @@
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.2215142778445382</v>
+        <v>-0.2526541886443173</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.3078579266745434</v>
+        <v>-0.2478634285731935</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4084014603163165</v>
+        <v>0.2355365841733175</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,28 +1703,28 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.188664555694396</v>
+        <v>-0.9228598385308522</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3326379815659699</v>
+        <v>0.193511835066392</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.084221184091953</v>
+        <v>0.4757423978722307</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.4061950358769124</v>
+        <v>0.05045451309524341</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,67 +1742,67 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.07421226479741944</v>
+        <v>0.001462217301187744</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1226216713878497</v>
+        <v>0.02091368144007015</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1825528783058658</v>
+        <v>0.002475289758745554</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.06564406692055859</v>
+        <v>-0.1558356005842687</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1052598541485273</v>
+        <v>-0.004327044041268426</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.6565397770243264</v>
+        <v>-0.669902014925837</v>
       </c>
       <c r="BW3" t="n">
         <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2065043550675515</v>
+        <v>0.07074030853022006</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.5632861499228645</v>
+        <v>0.3334871126674035</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1814,79 +1814,79 @@
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.3254296553724417</v>
+        <v>0.345384312224317</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.04616011975819771</v>
+        <v>-0.000526908071720324</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.2269095055632122</v>
+        <v>-0.1531811421063971</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1717409874268297</v>
+        <v>0.226783006211473</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.009807746280243213</v>
+        <v>-0.0893986005755418</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.02182886124040807</v>
+        <v>-0.1719006306269287</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.3081603552069221</v>
+        <v>0.3299978663699392</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01719092852330497</v>
+        <v>0.02127919723611408</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.2636827733883258</v>
+        <v>-0.1456998885722539</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,61 +1895,61 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1743738839238605</v>
+        <v>-0.008297665122839245</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.4081392467164909</v>
+        <v>0.2660152169800944</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.003652836732821756</v>
+        <v>-0.0200301860095748</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1159355303325251</v>
+        <v>0.1563961243562866</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.03783337820061265</v>
+        <v>0.01613528273854594</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.03552949308003384</v>
+        <v>-0.04966495023036537</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.19969548699952</v>
+        <v>-0.1618423516055258</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
@@ -1958,10 +1958,10 @@
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.191595629960169</v>
+        <v>0.1163863404652185</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.04199011987406678</v>
+        <v>0.091674285539548</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1970,25 +1970,25 @@
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2610369783493285</v>
+        <v>0.08653963632790217</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0816241501914651</v>
+        <v>0.1075112135154579</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.2019225802046823</v>
+        <v>-0.02273895078751852</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -2003,88 +2003,88 @@
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1356068046941536</v>
+        <v>0.186887512045581</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.001723912175921599</v>
+        <v>0.1316754654591585</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.06001921208959209</v>
+        <v>-0.04374862472988163</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2994629731993624</v>
+        <v>0.3658736941355334</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.003878327842907847</v>
+        <v>0.03797557760436729</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.2320757911727716</v>
+        <v>-0.1448486052212394</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1291452066174813</v>
+        <v>0.2606924883178133</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1435520906624544</v>
+        <v>0.02322608622299143</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.3925463397648482</v>
+        <v>-0.1960075495862793</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2618408833130081</v>
+        <v>0.3067421713448371</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,25 +2093,25 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.05611767305022519</v>
+        <v>-0.103411014684881</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.02958539890413955</v>
+        <v>-0.03156079513437525</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.08840376630044949</v>
+        <v>0.1200030648958258</v>
       </c>
       <c r="GA3" t="n">
         <v>-0</v>
@@ -2123,16 +2123,16 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.2849165325931532</v>
+        <v>-0.003829590812021398</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3866345650987164</v>
+        <v>0.510134480927237</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0652196549500524</v>
+        <v>-0.02317315160760532</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1852380084651767</v>
+        <v>-0.1253739700437799</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3589012147112821</v>
+        <v>0.752245188593158</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06311468071868366</v>
+        <v>-0.1885508715314557</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3651221592817521</v>
+        <v>-0.1678339080203445</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1094580176934663</v>
+        <v>0.2396801489690978</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,64 +2203,64 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07493545523177346</v>
+        <v>-0.1550645178228026</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04537530539723772</v>
+        <v>-0.02410377314521068</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02680376375963907</v>
+        <v>0.03359813872090403</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01825073112775779</v>
+        <v>-0.09489508163883574</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.004488947494421796</v>
+        <v>-0.05287303351191076</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09532539838076318</v>
+        <v>0.2745333803767226</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00415580200122351</v>
+        <v>0.1634374728456751</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.1346001625284309</v>
+        <v>-0.2268491839777776</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
@@ -2272,37 +2272,37 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.5030289018818075</v>
+        <v>1.091220677072524</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.1315890198888514</v>
+        <v>-0.3275860908385788</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.3211154406559409</v>
+        <v>-0.3515073625099807</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1325088011753167</v>
+        <v>-0.01796814793093769</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,43 +2311,43 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.09895809076854709</v>
+        <v>-0.134056749700401</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.06719795290494708</v>
+        <v>-0.0733891101654074</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1272550426278233</v>
+        <v>0.08137432507660729</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001543428793494194</v>
+        <v>0.1980451508661971</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.02834197504386468</v>
+        <v>0.002663628703968563</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>-0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2521749399794315</v>
+        <v>0.7901966277984974</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.09463853581078283</v>
+        <v>-0.1840896908271401</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1104589849583093</v>
+        <v>-0.2360193733155813</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2383,7 +2383,7 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1334336215203771</v>
+        <v>-0.3468040884577288</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,79 +2392,79 @@
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02750903240830612</v>
+        <v>0.05031868348433031</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1130399748392108</v>
+        <v>0.1550577490887936</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.009208760784757512</v>
+        <v>-0.3777219296855947</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.03142847188632505</v>
+        <v>0.2134092937630619</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.02608865444638875</v>
+        <v>0.2026030393924557</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1125354257182475</v>
+        <v>-0.3272563637820126</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01881686222551609</v>
+        <v>-0.004107552837681431</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.1285816063493219</v>
+        <v>0.1300902101041123</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.110943632860503</v>
+        <v>-0.03500019725909333</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
@@ -2473,64 +2473,64 @@
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05924378836863835</v>
+        <v>-0.2640672201424414</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.0781327605217683</v>
+        <v>-0.09624444256639834</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.02089521938103137</v>
+        <v>-0.1094779538443846</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.004531732174614046</v>
+        <v>-0.02619741750552691</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.01960440075622137</v>
+        <v>-0.01278670725710491</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.07880764562008102</v>
+        <v>0.1092180431086368</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03454565964938335</v>
+        <v>-0.07670621588935297</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.07168398243722526</v>
+        <v>-0.1162607643484133</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,25 +2542,25 @@
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0959036161817763</v>
+        <v>-0.05096223737680315</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.02756057177449348</v>
+        <v>-0.124987042922577</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.1179096359739856</v>
+        <v>0.05247735478366447</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
@@ -2569,37 +2569,37 @@
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.05661271075962738</v>
+        <v>-0.1892116993312313</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.03867075363098797</v>
+        <v>-0.1838854599527084</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.07324900669467149</v>
+        <v>0.09719161948642964</v>
       </c>
       <c r="EU4" t="n">
         <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1132900553736543</v>
+        <v>-0.3682751544074002</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
@@ -2608,52 +2608,52 @@
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02133329054558526</v>
+        <v>-0.007389888835078848</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.1171610192165286</v>
+        <v>0.1273841842789155</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.0418726762675006</v>
+        <v>-0.3629465976699605</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.04702444470215472</v>
+        <v>0.1994321184170075</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.105048327923058</v>
+        <v>0.130824887462705</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.01636650926019255</v>
+        <v>-0.09421733839058512</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,28 +2662,28 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0201023470847986</v>
+        <v>0.02573564981085936</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.05561454098591653</v>
+        <v>0.2206606386344299</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01046553829503089</v>
+        <v>-0.1336681604165663</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.0923712354584319</v>
+        <v>-0.09527424431893169</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1171522203616748</v>
+        <v>0.0118820498106034</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07769537784154766</v>
+        <v>-0.003253798049857726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01403027759955246</v>
+        <v>-0.0009532599433266761</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1072912980289972</v>
+        <v>0.01860293559166539</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,34 +3314,34 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07166815446829157</v>
+        <v>-0.01029728660843802</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.06128325757120401</v>
+        <v>-0.005690182837547014</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.103369047296544</v>
+        <v>0.008023209479981709</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05071431191825285</v>
+        <v>-0.009678666572573652</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
@@ -3350,25 +3350,25 @@
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0298550182338729</v>
+        <v>-0.003807520092918035</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.03223041025871016</v>
+        <v>-9.000947345274181e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.02019244749160701</v>
+        <v>-0.001947668249037561</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -3377,43 +3377,43 @@
         <v>-0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.007086456557502764</v>
+        <v>0.0012691824653067</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04375141117226868</v>
+        <v>0.006227063616836465</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02245480314480911</v>
+        <v>-0.0004440062528604215</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.01894393067596725</v>
+        <v>0.0003105117972520375</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2891945937456054</v>
+        <v>0.02766647119632201</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,25 +3422,25 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.05339141869602029</v>
+        <v>-0.01238783494660175</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.06169996504380463</v>
+        <v>-0.00465009440436462</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.04296874510369437</v>
+        <v>-0.004936534986797972</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1103950561165175</v>
+        <v>-0.007732308112455536</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.05456408347896312</v>
+        <v>0.0004802648060774828</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.09259187529615248</v>
+        <v>0.007545786935278249</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,16 +3476,16 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0350001516013413</v>
+        <v>0.009313971624906697</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01513760181454501</v>
+        <v>0.001756236775046453</v>
       </c>
       <c r="BT6" t="n">
         <v>-0</v>
@@ -3494,34 +3494,34 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1640321186132099</v>
+        <v>0.0180047122095656</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01621721108184061</v>
+        <v>-0.007223275391349716</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.04086317313890904</v>
+        <v>-0.005727109437366726</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.04005039453736143</v>
+        <v>-0.004879085073663173</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,7 +3530,7 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02312623059918093</v>
+        <v>0.002930774584608174</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
@@ -3539,34 +3539,34 @@
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.004960154156225826</v>
+        <v>0.0007787635248558353</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.03013559665652524</v>
+        <v>-0.005220958472171077</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.06824728127482101</v>
+        <v>0.009198954450465462</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.008255915511666868</v>
+        <v>0.001853146845881326</v>
       </c>
       <c r="CU6" t="n">
         <v>0</v>
@@ -3575,16 +3575,16 @@
         <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.02617137099424812</v>
+        <v>-0.00472877828929103</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.008103028067095468</v>
+        <v>0.002461754124577664</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3593,34 +3593,34 @@
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.004783080777824972</v>
+        <v>0.002859735662625968</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1341008557642005</v>
+        <v>-6.772133967996211e-05</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.004980297071295224</v>
+        <v>-0.004135368216590594</v>
       </c>
       <c r="DJ6" t="n">
         <v>0</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.03140617096667465</v>
+        <v>0.0007812014845062532</v>
       </c>
       <c r="DM6" t="n">
         <v>-0</v>
@@ -3629,7 +3629,7 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01030125214196313</v>
+        <v>-0.005601060091166336</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,25 +3638,25 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.00772217145140657</v>
+        <v>-0.005235341434612828</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.00397111530790464</v>
+        <v>0.001547746582648845</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.02986009251632469</v>
+        <v>0.005890664685835044</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,16 +3665,16 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.05060827884281158</v>
+        <v>-0.007929149487226089</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.02463985195862901</v>
+        <v>-0.003472218880915446</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,16 +3683,16 @@
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001186832841766219</v>
+        <v>-0.000168004159605919</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.05405793045737024</v>
+        <v>-0.003058085590850502</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,7 +3701,7 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.01132273647538058</v>
+        <v>-0.0006753335844687604</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,16 +3710,16 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04687477570126973</v>
+        <v>0.0008363166363169267</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01847597564686349</v>
+        <v>-0.002505253993154952</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
@@ -3728,16 +3728,16 @@
         <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.03681747963006655</v>
+        <v>0.002447395909923932</v>
       </c>
       <c r="EW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03042504632219524</v>
+        <v>-0.005547332671150434</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,7 +3746,7 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0001037867407597082</v>
+        <v>0.001025703622407463</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3755,16 +3755,16 @@
         <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.002845819723679651</v>
+        <v>0.002605065605073023</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.00067723714922764</v>
+        <v>-0.0002762269598316975</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,16 +3773,16 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.03170386045000795</v>
+        <v>0.007204136191809409</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0.03186899088181164</v>
+        <v>-0.002968709056187627</v>
       </c>
       <c r="FO6" t="n">
         <v>-0</v>
@@ -3791,7 +3791,7 @@
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.0004423759510849711</v>
+        <v>-0.0009865918755318052</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.006737069897284935</v>
+        <v>0.001974036341671114</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0.04845294949849172</v>
+        <v>0.002216685048000268</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.07956879762677511</v>
+        <v>-0.005499386375245662</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3836,27 +3836,27 @@
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0.04261807501368523</v>
+        <v>-0.0006049232994437387</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.1357483605627878</v>
+        <v>-0.0488525405605276</v>
       </c>
       <c r="B7" t="n">
-        <v>0.471545222356621</v>
+        <v>0.05741552958391704</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1184000133006523</v>
+        <v>-0.004322573270932714</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3871,22 +3871,22 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1095341113517893</v>
+        <v>-0.04311277864094578</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3509239546148908</v>
+        <v>0.08505339781865738</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2201235638612972</v>
+        <v>-0.004903720824678048</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,64 +3898,64 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01782538569656915</v>
+        <v>0.01077453653424605</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2808156362737016</v>
+        <v>0.01100519878970546</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0319595922127156</v>
+        <v>0.003743358954043791</v>
       </c>
       <c r="X7" t="n">
         <v>-0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.289197998188628e-11</v>
+        <v>-5.600659570097043e-12</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04006459550416364</v>
+        <v>0.002631542412140384</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01019858267952406</v>
+        <v>-0.006233789276640673</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.06171588043171918</v>
+        <v>-0.00513155518801875</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2291948306416728</v>
+        <v>0.02763008075276526</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,52 +3964,52 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.07473025865300924</v>
+        <v>-0.008840006300955178</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1003439603704824</v>
+        <v>-0.01733698413437168</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5676199226800873</v>
+        <v>0.07149748565518385</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.187371086190169</v>
+        <v>-0.02523161957208988</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
         <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0892895521631611</v>
+        <v>-0.04048774741432623</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02484930725929589</v>
+        <v>0.01265733878992723</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,13 +4018,13 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.3197824502166963</v>
+        <v>-0.01766180280746327</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>0</v>
@@ -4033,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.03689702504336245</v>
+        <v>0.009031189737577935</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.02966004789015406</v>
+        <v>0.02497182681622997</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,13 +4045,13 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0486838642217382</v>
+        <v>0.03142422371031091</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4060,22 +4060,22 @@
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.07345566494832846</v>
+        <v>0.00323166169918674</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.4399428602972525</v>
+        <v>0.06069252227420747</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01284693057299236</v>
+        <v>-0.003797701314797548</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4087,46 +4087,46 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.03846645660931336</v>
+        <v>0.0240460692253205</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1205331213713673</v>
+        <v>-0.02836369225641616</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.004452210365959581</v>
+        <v>-0.005481789585934684</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
         <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.1032579009833072</v>
+        <v>0.002882167016464611</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0147022360568047</v>
+        <v>-0.03720620553387993</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07180381608456735</v>
+        <v>0.006448504368644759</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
@@ -4138,22 +4138,22 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0158223023761332</v>
+        <v>0.02189377800083469</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1210588422898496</v>
+        <v>-0.02828303016338695</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01175359600926998</v>
+        <v>-0.01032678732536187</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4162,112 +4162,112 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.05663395425012152</v>
+        <v>0.01932697422255089</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.2237433202717032</v>
+        <v>-0.04356228359397669</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
         <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08276643242128741</v>
+        <v>-0.0251115608964448</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.06310804839520744</v>
+        <v>-0.009288317736758948</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.06499354676030347</v>
+        <v>-0.02053560333037056</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02238770425467532</v>
+        <v>0.002399613086582503</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.007604919893029321</v>
+        <v>0.01089283118136094</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.1088560744310052</v>
+        <v>0.02016895799054737</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.09295560656471952</v>
+        <v>0.01047642981715336</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0280664515375161</v>
+        <v>0.01668922564065249</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01490592077984777</v>
+        <v>-0.004857055780910359</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0008176124074175709</v>
+        <v>-0.01533739040072436</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,19 +4276,19 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.01199850614588686</v>
+        <v>0.01249296003110801</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.09958723909169671</v>
+        <v>-0.01249079962615636</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.00327027413583223</v>
+        <v>-0.01329036303113838</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
@@ -4297,43 +4297,43 @@
         <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0164381362783753</v>
+        <v>0.02611435662741643</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1307353684155892</v>
+        <v>-0.03566842577410072</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04560414542526635</v>
+        <v>-0.00947597176587868</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.03462099277012803</v>
+        <v>0.01422725189349505</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.07653719183352026</v>
+        <v>-0.0124215915156757</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
@@ -4342,7 +4342,7 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1068797934129631</v>
+        <v>0.004049732262889075</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4354,40 +4354,40 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>-0.03968380987151685</v>
+        <v>-0.007505123370199098</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.039867938709974</v>
+        <v>0.005115006844550455</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.008234770943463005</v>
+        <v>0.008038988047609889</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0.1101802597512309</v>
+        <v>0.007668252421368283</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02819735980326554</v>
+        <v>-0.01965718509073619</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
@@ -4396,19 +4396,19 @@
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4098900443988437</v>
+        <v>0.003246145938088831</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08227799030695876</v>
+        <v>-0.001527200389261162</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1604722546308923</v>
+        <v>-0.001158502601778101</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,22 +4443,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2794223289197117</v>
+        <v>0.004624020951653088</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1138799556426775</v>
+        <v>-0.001720084787927141</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1423336817695231</v>
+        <v>-0.001690238771849059</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -4470,88 +4470,88 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1524079558346236</v>
+        <v>0.0006969453066275674</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1057144407090385</v>
+        <v>-0.0009549024949279734</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.03065315048680929</v>
+        <v>-0.0001415100911127328</v>
       </c>
       <c r="Z8" t="n">
         <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.04597981453520556</v>
+        <v>4.404200376691617e-06</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00278627200385047</v>
+        <v>-0.0001020335567861844</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1.300750975096672e-12</v>
+        <v>1.840167941120933e-14</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.09490530666588119</v>
+        <v>0.001604726381523135</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.03287361078802519</v>
+        <v>0.0004323485535315282</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.0752632521930586</v>
+        <v>-0.0004133193889441389</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5262943068288627</v>
+        <v>0.005942893083874314</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,25 +4560,25 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.08213783715734063</v>
+        <v>-0.0004149777765591395</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.1029033420601003</v>
+        <v>-0.0006170956639976648</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07224892749850209</v>
+        <v>-0.001841515466882667</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,13 +4587,13 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1566819335878966</v>
+        <v>-0.001411455808358268</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.08862330491796601</v>
+        <v>-0.0001788603181808363</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
@@ -4602,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.01903338426589549</v>
+        <v>0.0004278732613613894</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,13 +4614,13 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.09855255477021753</v>
+        <v>0.003131629111873912</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.06142185439939696</v>
+        <v>0.0003713864175881696</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,34 +4632,34 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2440550821483009</v>
+        <v>0.004189769808260179</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0001067524158789265</v>
+        <v>-0.0008543034022637125</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA8" t="n">
-        <v>-0.04890422322457139</v>
+        <v>-0.0004146378677923059</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1180164843711058</v>
+        <v>-0.001653726510168594</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,13 +4668,13 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0002147394170136029</v>
+        <v>0.0007636445395584998</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.05404896621148526</v>
+        <v>0.0002087748291688786</v>
       </c>
       <c r="CK8" t="n">
         <v>-0</v>
@@ -4683,10 +4683,10 @@
         <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.05571621167399746</v>
+        <v>-0.001462240595665281</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
@@ -4695,13 +4695,13 @@
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.06379555282570942</v>
+        <v>0.0001787981318005017</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.009798578260283432</v>
+        <v>-0.0005871936154300452</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
@@ -4710,10 +4710,10 @@
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1106735706611887</v>
+        <v>-0.001773862903330104</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.004626446785627507</v>
+        <v>0.0005327749870042511</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.05954125072354864</v>
+        <v>0.0005128328706557613</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.2577705968754488</v>
+        <v>-0.0008134443995798789</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
@@ -4749,52 +4749,52 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05676800317147357</v>
+        <v>-0.0006387282976606317</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0.04572640180826062</v>
+        <v>-0.0005509655906947051</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0186753328669094</v>
+        <v>-0.0005558317232563456</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.01057363926653227</v>
+        <v>0.0002223652360671881</v>
       </c>
       <c r="DS8" t="n">
         <v>-0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.01706972545431486</v>
+        <v>0.0005083824635174211</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.08513952644225262</v>
+        <v>0.001235515983783688</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,13 +4803,13 @@
         <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.04212632996419635</v>
+        <v>-0.0007586093475600698</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.007186996227142493</v>
+        <v>0.0001573696483515261</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -4818,25 +4818,25 @@
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.04469998879471928</v>
+        <v>-0.001058619275289009</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.03184625342459373</v>
+        <v>0.0004683860430682178</v>
       </c>
       <c r="EK8" t="n">
         <v>-0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.04868115966043891</v>
+        <v>-0.0002370635914775763</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4848,22 +4848,22 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.07096211506215327</v>
+        <v>-0.001164700987408045</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02246581162229058</v>
+        <v>-0.0003289322881345127</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0.02248952459950865</v>
+        <v>-0.0002314257668706953</v>
       </c>
       <c r="EV8" t="n">
         <v>-0</v>
@@ -4872,10 +4872,10 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1151516076051104</v>
+        <v>-0.001958588011594377</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
@@ -4884,13 +4884,13 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.02033570527087088</v>
+        <v>0.0003676609312450939</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.06151894651262665</v>
+        <v>0.0002346836571444418</v>
       </c>
       <c r="FE8" t="n">
         <v>-0</v>
@@ -4899,37 +4899,37 @@
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.08161482493172421</v>
+        <v>-0.0004561763322339462</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.06190685197872927</v>
+        <v>0.0003672679324081981</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.03084676356172001</v>
+        <v>7.4581032514135e-05</v>
       </c>
       <c r="FN8" t="n">
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01597373766650189</v>
+        <v>-7.236693279895649e-05</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,28 +4938,28 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.007080682751813538</v>
+        <v>0.0002781047125355201</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.05367644865522656</v>
+        <v>0.0004845635353959671</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.07605121471279719</v>
+        <v>-0.001528225738202969</v>
       </c>
       <c r="GA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,16 +4968,16 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
-        <v>-0.09427837772574504</v>
+        <v>0.0007248185530438483</v>
       </c>
       <c r="GF8" t="n">
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5957070299934158</v>
+        <v>1.185217597296268</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1696867093349326</v>
+        <v>-0.5087076615946142</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,13 +5006,13 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2339278100894732</v>
+        <v>-0.125063679014855</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448974670023354</v>
+        <v>1.482964424584295</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2058805598437507</v>
+        <v>-0.5765215076393559</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,106 +5030,106 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.2173415236387826</v>
+        <v>-0.08809681896325477</v>
       </c>
       <c r="S9" t="n">
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2123233266226793</v>
+        <v>0.2951793319845037</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00385825139451771</v>
+        <v>-0.2057084370601451</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
         <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.04436097778096185</v>
+        <v>-0.2971439742375101</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05839711786124133</v>
+        <v>0.0370682782749094</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01209987869598493</v>
+        <v>-0.08924349905081934</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.005791483618786395</v>
+        <v>0.01813520234109972</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.134595462251407</v>
+        <v>0.647218271977446</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002605866371041171</v>
+        <v>0.3151340337522126</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.04072840051334569</v>
+        <v>-0.01990357901397147</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6524579953298536</v>
+        <v>1.906082763680571</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.06351245641272907</v>
+        <v>-0.3466726432555277</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -5138,16 +5138,16 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.1647765097551635</v>
+        <v>0.05734532317016303</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1373202862337907</v>
+        <v>-0.4187780066644352</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,25 +5156,25 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2926253679172579</v>
+        <v>-0.4664721796651017</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.1399409036545141</v>
+        <v>-0.06902629970221594</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.03139032031344098</v>
+        <v>0.1100041437924637</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,25 +5183,25 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.2181287444900121</v>
+        <v>0.2565249993184942</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0.005477750310742354</v>
+        <v>0.1790245898771092</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.4078918779930873</v>
+        <v>1.316920678674573</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,25 +5210,25 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04297685847085359</v>
+        <v>-0.2710160758287363</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0.05803283620738584</v>
+        <v>-0.2159210613528768</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1662124194299424</v>
+        <v>-0.6714875314215168</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
@@ -5237,34 +5237,34 @@
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.003134508757096788</v>
+        <v>0.1400475975698884</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0994535199869427</v>
+        <v>0.07077091264935598</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.1079344122890634</v>
+        <v>-0.586243147508054</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.06457839891453634</v>
+        <v>0.1040190846400225</v>
       </c>
       <c r="CR9" t="n">
         <v>-0</v>
@@ -5276,40 +5276,40 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.01189848822070122</v>
+        <v>0.01263317585704447</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1435100062129844</v>
+        <v>-0.6460743325784353</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.002914210024429154</v>
+        <v>0.09994976969990746</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.08346824965068411</v>
+        <v>0.1365030123987227</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.2757533220253617</v>
+        <v>-0.2650128418010136</v>
       </c>
       <c r="DG9" t="n">
         <v>-0</v>
@@ -5318,7 +5318,7 @@
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03742216675639115</v>
+        <v>0.001188408820893325</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5327,25 +5327,25 @@
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.03382726213238105</v>
+        <v>-0.1527310611334255</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.0524889167509658</v>
+        <v>-0.282372928175631</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01897198861855883</v>
+        <v>0.02527764099881244</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5354,43 +5354,43 @@
         <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0.02259084022748285</v>
+        <v>-0.2682034397995977</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.1287055737378587</v>
+        <v>0.4311930797098074</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04856352747623631</v>
+        <v>-0.2688737073820104</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0.002166771162325189</v>
+        <v>0.2437364332092798</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03605802408271335</v>
+        <v>-0.2927423262201128</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
@@ -5399,52 +5399,52 @@
         <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03003494941585363</v>
+        <v>-0.04079657010266549</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.137731513553764</v>
+        <v>0.05303673578530386</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1294142052476756</v>
+        <v>-0.4327857021338016</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01001814084406722</v>
+        <v>-0.01332497492532339</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.04018003600841379</v>
+        <v>0.1350836462168304</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1730053009386717</v>
+        <v>-0.7478174870713271</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
@@ -5453,25 +5453,25 @@
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.006680594824809261</v>
+        <v>0.08283698895017998</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.08106363987243112</v>
+        <v>0.1358316440088084</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.09365301958237854</v>
+        <v>-0.2786981191275719</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,25 +5480,25 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.07364333820539103</v>
+        <v>-0.06168781112966576</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>-0.08289972846443332</v>
+        <v>-0.2170243165505544</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.02461631250917898</v>
+        <v>-0.06394074838965132</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
@@ -5507,46 +5507,46 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.005662067530327327</v>
+        <v>0.05679715598349662</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.02765675302878911</v>
+        <v>-0.2717723594668973</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.1405516112716614</v>
+        <v>-0.3220315751040938</v>
       </c>
       <c r="GA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0.02207852803345344</v>
+        <v>0.1561356267870529</v>
       </c>
     </row>
     <row r="10">
@@ -6120,19 +6120,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.5856001959820877</v>
+        <v>-0.6478942283082595</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5022069967477493</v>
+        <v>0.2914116423392542</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2019405168929685</v>
+        <v>0.3573365100021121</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -6150,25 +6150,25 @@
         <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4466406107400447</v>
+        <v>-0.8491449388215113</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3649670802807409</v>
+        <v>0.2614971367250337</v>
       </c>
       <c r="M11" t="n">
         <v>-0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3209053489582296</v>
+        <v>0.2832491774173554</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,16 +6177,16 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1810590841102909</v>
+        <v>-0.2040824869085449</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01800573941513638</v>
+        <v>-0.1381991078588617</v>
       </c>
       <c r="V11" t="n">
         <v>-0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.03597234547544773</v>
+        <v>-0.0828647371651253</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -6195,52 +6195,52 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.08992670870348285</v>
+        <v>-0.0306019591384103</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001589339339085907</v>
+        <v>0.1015001184864049</v>
       </c>
       <c r="AE11" t="n">
         <v>-0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02538595015608277</v>
+        <v>0.03204285376171379</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.3067323077130655</v>
+        <v>-0.3807231062937763</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0530606601333064</v>
+        <v>0.04619011503155655</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02159134968205524</v>
+        <v>-0.3623431556318693</v>
       </c>
       <c r="AP11" t="n">
         <v>-0</v>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
         <v>-0</v>
@@ -6258,46 +6258,46 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.617233362100586</v>
+        <v>-1.009051285480639</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.3770445913161772</v>
+        <v>-0.02373168421458201</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0224074979188193</v>
+        <v>-0.06240384275433162</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.1065925556001996</v>
+        <v>0.4377223722174859</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.1608053621663371</v>
+        <v>0.2902703894315217</v>
       </c>
       <c r="BF11" t="n">
         <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.4640094995812941</v>
+        <v>0.6512330149958828</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
@@ -6312,25 +6312,25 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.1452236846289819</v>
+        <v>0.02056988638582829</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.09469487937371532</v>
+        <v>-0.02460740961295904</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.06245659527023845</v>
+        <v>-0.03891897386786528</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -6339,16 +6339,16 @@
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.2765555048289</v>
+        <v>-0.6579446257966903</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.4013442095394716</v>
+        <v>-0.03467811699314138</v>
       </c>
       <c r="BX11" t="n">
         <v>-0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.004434337996179909</v>
+        <v>-0.04505153753157709</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -6360,31 +6360,31 @@
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.1432574306917467</v>
+        <v>0.379892055062188</v>
       </c>
       <c r="CF11" t="n">
-        <v>-0.05865092973877033</v>
+        <v>-0.1025571504782499</v>
       </c>
       <c r="CG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.07377024584961395</v>
+        <v>-0.09181980681504485</v>
       </c>
       <c r="CI11" t="n">
         <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,16 +6393,16 @@
         <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.04580832386164815</v>
+        <v>0.3089989689802744</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.009052390728214236</v>
+        <v>-0.03721175094642184</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1053647506541834</v>
+        <v>-0.1518825861966959</v>
       </c>
       <c r="CR11" t="n">
         <v>0</v>
@@ -6420,16 +6420,16 @@
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.08292950891231435</v>
+        <v>0.349247143794073</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0.05278747009344598</v>
+        <v>-0.08115513609193273</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.03297007351594661</v>
+        <v>-0.06810017084170526</v>
       </c>
       <c r="DA11" t="n">
         <v>-0</v>
@@ -6438,7 +6438,7 @@
         <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>-0</v>
@@ -6447,16 +6447,16 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.1128864293612076</v>
+        <v>0.04984562520329686</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0698839246658456</v>
+        <v>0.03348037149164617</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09902490285184505</v>
+        <v>0.02583563876850147</v>
       </c>
       <c r="DJ11" t="n">
         <v>0</v>
@@ -6468,52 +6468,52 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0009514928174906399</v>
+        <v>0.159293761961485</v>
       </c>
       <c r="DP11" t="n">
-        <v>-0.04621032599136168</v>
+        <v>-0.06185794293549377</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.1014787998134182</v>
+        <v>-0.06252070506743891</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.0147438247669354</v>
+        <v>-0.2443349539639854</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.1214368583341717</v>
+        <v>-0.03389683314347385</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.09464167323103202</v>
+        <v>0.2116493629259438</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
@@ -6525,46 +6525,46 @@
         <v>0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.04739073703616527</v>
+        <v>0.2165696301693601</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0.03314198676337968</v>
+        <v>0.09452352555514176</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.1130302533890585</v>
+        <v>-0.07416220991878822</v>
       </c>
       <c r="EK11" t="n">
         <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM11" t="n">
         <v>0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.02784314165513375</v>
+        <v>0.2551823004371448</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.09325877213996679</v>
+        <v>0.07383431355915128</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.04580871629295503</v>
+        <v>-0.01117261186294968</v>
       </c>
       <c r="ET11" t="n">
         <v>0</v>
@@ -6573,34 +6573,34 @@
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.09084816304900233</v>
+        <v>0.419585384286311</v>
       </c>
       <c r="EZ11" t="n">
-        <v>-0.04808789099140418</v>
+        <v>-0.08824167977884338</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05293122716942122</v>
+        <v>-0.09549401757295148</v>
       </c>
       <c r="FC11" t="n">
         <v>0</v>
       </c>
       <c r="FD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>0</v>
@@ -6609,70 +6609,70 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.1511096807473324</v>
+        <v>0.08501947467815164</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.1640419176618498</v>
+        <v>0.2445605977325841</v>
       </c>
       <c r="FJ11" t="n">
         <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.2202719246022012</v>
+        <v>0.2305485915617206</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP11" t="n">
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.000122649232929846</v>
+        <v>0.001557106707699393</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0.06476043956903237</v>
+        <v>-0.005335269013560164</v>
       </c>
       <c r="FS11" t="n">
         <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01150767731223456</v>
+        <v>-0.02131421605597281</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
         <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.09324930545369339</v>
+        <v>0.1887370741972324</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0.03898125574773053</v>
+        <v>0.2030959035761905</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>-0</v>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1719540176490533</v>
+        <v>0.3100159468294384</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05510748947682456</v>
+        <v>0.06811120432950202</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08715665807871681</v>
+        <v>-0.1611041023914769</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1390656461686944</v>
+        <v>0.3933133250076254</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,16 +6728,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02624024872693008</v>
+        <v>-0.05829223161404149</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07232889606455117</v>
+        <v>-0.1864319653107201</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,49 +6746,49 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02727864124550647</v>
+        <v>0.1339420394090474</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01982417378577795</v>
+        <v>-0.04676546405744341</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00177633182022937</v>
+        <v>-0.0005520063346231733</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.003768989232316697</v>
+        <v>-0.01381869985767347</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00501737195938803</v>
+        <v>-0.06484855263153887</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002169836679830884</v>
+        <v>0.01799787771950286</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,34 +6800,34 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02590748447132112</v>
+        <v>0.08563412067092957</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0008909777968175589</v>
+        <v>-0.03916690223177431</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.04164852344248137</v>
+        <v>-0.04927568746796703</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1271298540695137</v>
+        <v>0.582070555182156</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.03770247805047881</v>
+        <v>-0.2317705639356958</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.09526868018307566</v>
+        <v>-0.2360066015405801</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03604310439482949</v>
+        <v>-0.1412913627122537</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,106 +6863,106 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03919740946567946</v>
+        <v>0.01172857157645602</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.02183761878672415</v>
+        <v>-0.06330069356572139</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03191466590888783</v>
+        <v>0.1317949683534462</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.003310019553334726</v>
+        <v>0.07966873889276965</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.008157693347078132</v>
+        <v>0.02499458703803637</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.07007692543435005</v>
+        <v>0.311414107391049</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.02844187206118379</v>
+        <v>-0.05773175388937433</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.02748117557111489</v>
+        <v>-0.09267839471568112</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.03525370561808943</v>
+        <v>-0.1264526959990391</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0008299013390268792</v>
+        <v>0.01543443378994865</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.02571409301663053</v>
+        <v>0.04786293207660536</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.003508196526299338</v>
+        <v>-0.1484235205822863</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,37 +6971,37 @@
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.003662989812347138</v>
+        <v>0.1087592152210064</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02252779228620241</v>
+        <v>0.03336387973319571</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03222189101000417</v>
+        <v>-0.1203053099527209</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002035440516834429</v>
+        <v>-0.009253540863334591</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.03141525101889747</v>
+        <v>0.08180846623758554</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7010,40 +7010,40 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.02464504027803544</v>
+        <v>-0.1166518942729981</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04390092452442424</v>
+        <v>-0.1717712997393305</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.000415718521753898</v>
+        <v>0.05067825537158664</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0112438305052271</v>
+        <v>-0.06995829549528715</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
@@ -7052,37 +7052,37 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01783998545642576</v>
+        <v>0.01555041194180345</v>
       </c>
       <c r="DS12" t="n">
-        <v>-1.520451815036939e-05</v>
+        <v>0.07062148928896106</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.02362827017215603</v>
+        <v>-0.1114566189214003</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.006528698083716571</v>
+        <v>0.009111141093780377</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.012803167295742</v>
+        <v>0.02823263846278938</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,25 +7091,25 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03508480927577015</v>
+        <v>-0.0354489578088179</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01182183706424115</v>
+        <v>-0.03623872431755571</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.03338423356741664</v>
+        <v>-0.03767154240204373</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7124,22 +7124,22 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0211354864433247</v>
+        <v>-0.0130880037112671</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.007802926414176778</v>
+        <v>-0.08802217275359603</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.006600795818346028</v>
+        <v>-0.01793812027157698</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,46 +7151,46 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02995722307648519</v>
+        <v>-0.1512773396245544</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.002203834215592546</v>
+        <v>-0.0127472065120183</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02706645431695889</v>
+        <v>0.0604761911094209</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.001231492219864073</v>
+        <v>0.09690481661052079</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.009410707390329997</v>
+        <v>-0.02623287152169475</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.02954821090179123</v>
+        <v>0.1271336068629508</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
@@ -7202,10 +7202,10 @@
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.001983613360450768</v>
+        <v>-0.02284104427554435</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,43 +7214,43 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01128133942941411</v>
+        <v>0.06178755696227989</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01844022066727466</v>
+        <v>-0.09293733920215562</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.005415781100468099</v>
+        <v>-0.04592804335817525</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.02005812897815362</v>
+        <v>0.08713129147864047</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1057968697325088</v>
+        <v>0.169065790212127</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,37 +7270,37 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.08475484688763088</v>
+        <v>-0.05066034267543727</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02057865388933401</v>
+        <v>-0.0492492105172555</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07480445114314249</v>
+        <v>0.1865473395647892</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.06648916123669923</v>
+        <v>-0.08425672573086003</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.02522494392780352</v>
+        <v>-0.06334587307873651</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7312,49 +7312,49 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01906094125911958</v>
+        <v>0.06023724467500365</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.004191752753759134</v>
+        <v>-0.05267309116892206</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01180110368614054</v>
+        <v>0.002023197367531834</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.003272045536479402</v>
+        <v>-0.01760236852532795</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.002587517684227683</v>
+        <v>-0.0577588608007779</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00231735278533981</v>
+        <v>0.005667795359072101</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7366,37 +7366,37 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01806452962940453</v>
+        <v>0.01907790185305228</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01243386786388016</v>
+        <v>-0.03279324789573839</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01228520317475038</v>
+        <v>0.006009324699997425</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.09027327901085329</v>
+        <v>0.2047505535943754</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.05113521881706509</v>
+        <v>-0.122566255077423</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.01129680401635391</v>
+        <v>-0.0875325502405213</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01919559861795131</v>
+        <v>-0.02164178361000426</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,64 +7432,64 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.04969339796314527</v>
+        <v>-0.01232337492912886</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.01919363218217901</v>
+        <v>-0.00444542915371853</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02558812258889233</v>
+        <v>0.03142857731603116</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.01396521779819443</v>
+        <v>0.05551157567144697</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0217762928690108</v>
+        <v>0.002868336026333868</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04866710589721925</v>
+        <v>0.1262015038498201</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02364773077474541</v>
+        <v>-0.04144153277037738</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.001996118077983738</v>
+        <v>-0.02918084037244212</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,34 +7504,34 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01760819412881975</v>
+        <v>-0.04432926185321448</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01222752609177812</v>
+        <v>0.02828454650189088</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.007245793073079688</v>
+        <v>0.02244905793340447</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.0002141957200115257</v>
+        <v>-0.0318874636945167</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,40 +7540,40 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.003925178938257989</v>
+        <v>0.05526558969804204</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.003646202967627068</v>
+        <v>0.01671105001416602</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.01094687758772159</v>
+        <v>-0.04542752808449991</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.009415954308945634</v>
+        <v>0.02493848444848961</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01312032000253682</v>
+        <v>0.03762893299077263</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.01631896342086048</v>
+        <v>-0.03983530717061545</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01846983431862562</v>
+        <v>-0.04095832388797412</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.003693580578417738</v>
+        <v>0.0159250373701761</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7606,40 +7606,40 @@
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.008041331963759196</v>
+        <v>0.007897533915924355</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01979462192430372</v>
+        <v>-0.02882831525024543</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01366813514594768</v>
+        <v>-0.001330311087722285</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01512565863019831</v>
+        <v>-0.01099574836975101</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,16 +7648,16 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01340477666797229</v>
+        <v>-0.01852168617847985</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.001415198527650156</v>
+        <v>-0.001732339243399531</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,22 +7666,22 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01793955233745228</v>
+        <v>-0.0262911255668647</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01082317761302391</v>
+        <v>0.02437037433461773</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.007110880765519101</v>
+        <v>0.0006051399637435671</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7693,19 +7693,19 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0003538967037369907</v>
+        <v>-0.03077126215995603</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.008469124541862586</v>
+        <v>0.02736314960902176</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.001591717708135629</v>
+        <v>0.05143346906447127</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,25 +7714,25 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.01113163272902852</v>
+        <v>-0.05209393238056755</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.01147713504073795</v>
+        <v>0.01799644510432529</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0145324386488448</v>
+        <v>0.02306254443938176</v>
       </c>
       <c r="FD13" t="n">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.002715196563887185</v>
+        <v>0.05484359754724453</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01351145408553161</v>
+        <v>-0.03642639001315871</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01047446064001669</v>
+        <v>0.04090037014279284</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,52 +7774,52 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.002701188916824334</v>
+        <v>-0.0167414066059839</v>
       </c>
       <c r="FR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.008326859423344778</v>
+        <v>0.02974479920288671</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0120175413229906</v>
+        <v>-0.03288490210535657</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.0005504205876127753</v>
+        <v>-0.04698836091928854</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01311505274425613</v>
+        <v>0.04041042830583202</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,46 +7830,46 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4153572051450508</v>
+        <v>0.2561772895102798</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1527524371230786</v>
+        <v>-0.1750014830929682</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05337349798471756</v>
+        <v>-0.01707228129826151</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3239443995061827</v>
+        <v>0.3310243202847041</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1895680220001493</v>
+        <v>-0.2530986344472804</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.06892823910276677</v>
+        <v>-0.07292901125943244</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -7881,22 +7881,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.102082386197136</v>
+        <v>0.05356350450260748</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01067781167138243</v>
+        <v>-0.04687319317016449</v>
       </c>
       <c r="W14" t="n">
-        <v>0.09840651620137804</v>
+        <v>-0.03705709661439411</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7905,49 +7905,49 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1042984366478261</v>
+        <v>-0.0168642603143915</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.008280249905984419</v>
+        <v>-0.02899412825898812</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.007868876847546148</v>
+        <v>-0.0150814432286299</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.01413306067264882</v>
+        <v>0.05757216167317508</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06963297121984609</v>
+        <v>-0.06238822091384541</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.09327890535983155</v>
+        <v>0.03596742762678435</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7959,31 +7959,31 @@
         <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3350417824791784</v>
+        <v>0.2404149541552711</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.0582899494006054</v>
+        <v>-0.145423785059637</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1352134909149114</v>
+        <v>-0.1338746695358506</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,25 +7992,25 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03028057937233576</v>
+        <v>-0.007752149394776846</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.06014711045112877</v>
+        <v>-0.04414746632039725</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1089048352468886</v>
+        <v>0.02384365208788119</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,16 +8019,16 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.05861349550282345</v>
+        <v>-0.0008410011251675629</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0575667306426512</v>
+        <v>0.09645894003761352</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1982779608751278</v>
+        <v>0.01307952018555015</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
@@ -8040,55 +8040,55 @@
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1635072823828878</v>
+        <v>0.1698814881300876</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01661427909170024</v>
+        <v>-0.1458391754460469</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09747195118235644</v>
+        <v>-0.005598778551234183</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.09299382153137263</v>
+        <v>-0.07666697059516209</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02466341910762236</v>
+        <v>0.1084906814593476</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01222205628045068</v>
+        <v>0.008496451031540524</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,49 +8100,49 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.03087720610851103</v>
+        <v>-0.07823351359508972</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.07622409350281764</v>
+        <v>0.1166813786195598</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.136309073103893</v>
+        <v>0.04055031482710982</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.08923844109489036</v>
+        <v>-0.08682244662341965</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.04471339974487957</v>
+        <v>0.1254738101017041</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.004810092314039812</v>
+        <v>0.01084953685973634</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
@@ -8154,16 +8154,16 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.008880697775690335</v>
+        <v>-0.02695985563480279</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.003708755479479001</v>
+        <v>0.01093239612189692</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.002878872980683219</v>
+        <v>-0.03487059043924402</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8178,22 +8178,22 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.01040306623990542</v>
+        <v>-0.07519457440914891</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.1684177412083869</v>
+        <v>0.0438662129144749</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03684732392055023</v>
+        <v>0.01566541962965003</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
@@ -8202,82 +8202,82 @@
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.06528869013948503</v>
+        <v>-0.003432475501874451</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.01647540544408062</v>
+        <v>-0.01314104424326174</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01696301540797479</v>
+        <v>-0.03449910040350194</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1170385087711713</v>
+        <v>-0.05154199724513816</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.08252476119456385</v>
+        <v>0.07848901072739527</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.07755929381076397</v>
+        <v>0.0348342930062163</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.08683023244737859</v>
+        <v>-0.02209216035294274</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.06773080070714632</v>
+        <v>0.07825511185941922</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01989386463468211</v>
+        <v>-0.01497028819188232</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,46 +8286,46 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.08395258427681976</v>
+        <v>-0.09368032424183863</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02768983226285621</v>
+        <v>0.123554136443522</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.004075162106430106</v>
+        <v>0.01331652200640048</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.02981761782796473</v>
+        <v>0.0692475196620234</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.07811525575997685</v>
+        <v>-0.1447210542788393</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.03957293323877484</v>
+        <v>0.01484784457313872</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8337,22 +8337,22 @@
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.006028435789170863</v>
+        <v>-0.04293328085521802</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.1084392961027306</v>
+        <v>0.07866008797769514</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.005669346021173258</v>
+        <v>0.03681617316414271</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,37 +8361,37 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.01330668224531322</v>
+        <v>-0.0165711092709719</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.0646767419494222</v>
+        <v>0.0345974475000691</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8968,19 +8968,19 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1955844602962666</v>
+        <v>0.7878633203216263</v>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0573237275039872</v>
+        <v>0.1753757439169801</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1176689356884328</v>
+        <v>-0.2848025707500379</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8989,40 +8989,40 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1725380383146246</v>
+        <v>1.052020991432592</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03145811373663959</v>
+        <v>-0.02868449116591235</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1173016771310044</v>
+        <v>-0.2635062595567315</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02088460486761182</v>
+        <v>0.2079886283190378</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,16 +9031,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01640005628446425</v>
+        <v>-0.08988934089694015</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.001993725783814916</v>
+        <v>-0.03733567909227709</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -9049,22 +9049,22 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.001356453217562624</v>
+        <v>0.02773102369761076</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01935586411750067</v>
+        <v>-0.3836868560917128</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.0002807767392033485</v>
+        <v>-0.06763825322011548</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02453327275050268</v>
+        <v>0.1946461235988402</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.004011956251488029</v>
+        <v>0.004040885704422371</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.03186811951592929</v>
+        <v>-0.088055344967441</v>
       </c>
       <c r="AQ16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1182207341344241</v>
+        <v>0.9356747488995848</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,79 +9112,79 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.01706000986491803</v>
+        <v>-0.2145807810634514</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.0622545558779858</v>
+        <v>-0.1358086835724432</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03487884350627186</v>
+        <v>-0.09620385774168327</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04686936049584645</v>
+        <v>-0.1128013532478385</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.04431923995765664</v>
+        <v>-0.1497521574502735</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03312529975264238</v>
+        <v>0.1497531676924427</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.003557253501918739</v>
+        <v>0.02932298932774973</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01915244502906337</v>
+        <v>-0.04570139209666776</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0602171278281084</v>
+        <v>0.5668626715363552</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01864234103097717</v>
+        <v>-0.03867182932408814</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.04035080286368642</v>
+        <v>-0.1926619328002012</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9211,154 +9211,154 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03091895479689228</v>
+        <v>-0.2621310381608715</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.002999741711921904</v>
+        <v>0.03875378378788715</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02745837148458497</v>
+        <v>0.1125435231158723</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.00736323709553628</v>
+        <v>-0.4206053496293856</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01337612968087371</v>
+        <v>0.2412518257946932</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.008538606990017008</v>
+        <v>0.1373299599268796</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02406000500622384</v>
+        <v>-0.2355637327233895</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.006775498304454394</v>
+        <v>-0.02538272437477521</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03280272960414036</v>
+        <v>0.144313813824928</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.01228768337052847</v>
+        <v>-0.05974332068089105</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.03094020918752625</v>
+        <v>-0.3772494412608997</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001226839614979743</v>
+        <v>0.0705458071498398</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.006795211005618329</v>
+        <v>-0.1019115115004232</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0307923293361752</v>
+        <v>0.0009387559614029015</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0004612995519719142</v>
+        <v>-0.03777027794315943</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.01377460250652974</v>
+        <v>-0.03195515761340013</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.004741634155976387</v>
+        <v>-0.2125355220908846</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01780713693393893</v>
+        <v>0.1005985311688274</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
@@ -9370,37 +9370,37 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03293124787782795</v>
+        <v>-0.06804950097864934</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.00304971769285448</v>
+        <v>-0.1232623316891327</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.02741264553479034</v>
+        <v>0.0244671423088197</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01162491910939762</v>
+        <v>-0.05713902585655186</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
@@ -9409,70 +9409,70 @@
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.01449646432241165</v>
+        <v>-0.1078659820456623</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.01451631036138486</v>
+        <v>0.04829185494511695</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.02235811953906987</v>
+        <v>-0.2770526568463335</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.004649318084795771</v>
+        <v>-0.06955994564503337</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03077857441642638</v>
+        <v>0.1307979196548326</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.002722592043912259</v>
+        <v>0.3173173310531133</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.008630068950705883</v>
+        <v>-0.1927178963482096</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.02239772934934034</v>
+        <v>-0.2770468636342763</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.003555128235483988</v>
+        <v>-0.1569485778581266</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,46 +9490,46 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.003938254028870664</v>
+        <v>0.07158514427785638</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.03465978461921009</v>
+        <v>-0.2219408003871606</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01840337407645683</v>
+        <v>0.02764576239744682</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.01639096137968626</v>
+        <v>0.05844353895394877</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
